--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>127133743</v>
       </c>
       <c r="B8" t="n">
-        <v>43278</v>
+        <v>43282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>127133743</v>
       </c>
       <c r="B8" t="n">
-        <v>43282</v>
+        <v>43284</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>127133743</v>
       </c>
       <c r="B8" t="n">
-        <v>43284</v>
+        <v>43285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>127133743</v>
       </c>
       <c r="B8" t="n">
-        <v>43285</v>
+        <v>43278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -1408,7 +1408,7 @@
         <v>127133743</v>
       </c>
       <c r="B8" t="n">
-        <v>43278</v>
+        <v>43285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51923-2022 artfynd.xlsx
+++ b/artfynd/A 51923-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108969120</v>
+        <v>104636279</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Logårdsäng, Sm</t>
+          <t>A 51923, Edsbruk, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585715.1738902844</v>
+        <v>585709</v>
       </c>
       <c r="R2" t="n">
-        <v>6433410.738051517</v>
+        <v>6433314</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,33 +775,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108965072</v>
+        <v>108969120</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +805,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skoghall, Sm</t>
+          <t>Logårdsäng, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586002.605345579</v>
+        <v>585716</v>
       </c>
       <c r="R3" t="n">
-        <v>6433124.017261685</v>
+        <v>6433410</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109513964</v>
+        <v>108974819</v>
       </c>
       <c r="B4" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,49 +913,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51923, Edsbruk, Sm</t>
+          <t>Skoghall, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585534.2691037513</v>
+        <v>585841</v>
       </c>
       <c r="R4" t="n">
-        <v>6433581.635057534</v>
+        <v>6433177</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,84 +992,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109514029</v>
+        <v>127133743</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>101509</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51923, Edsbruk, Sm</t>
+          <t>NV Solbacken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585673.2104089177</v>
+        <v>586095</v>
       </c>
       <c r="R5" t="n">
-        <v>6433437.378088964</v>
+        <v>6433125</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,34 +1103,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Roine Strandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Roine Strandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Apollofjäril</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109514010</v>
+        <v>108968927</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,53 +1136,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 51923, Edsbruk, Sm</t>
+          <t>Logårdsäng, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585604.7728336727</v>
+        <v>585649</v>
       </c>
       <c r="R6" t="n">
-        <v>6433461.33128516</v>
+        <v>6433421</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,22 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,34 +1215,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109513989</v>
+        <v>109513964</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,16 +1244,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>219686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,15 +1263,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1332,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585527.4455641559</v>
+        <v>585534</v>
       </c>
       <c r="R7" t="n">
-        <v>6433553.418161711</v>
+        <v>6433582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,19 +1313,9 @@
           <t>2023-05-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,62 +1343,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127133743</v>
+        <v>108965072</v>
       </c>
       <c r="B8" t="n">
-        <v>43285</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101509</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollofjäril</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parnassius apollo</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NV Solbacken, Sm</t>
+          <t>Skoghall, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586095</v>
+        <v>586003</v>
       </c>
       <c r="R8" t="n">
         <v>6433125</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,12 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,19 +1429,565 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roine Strandberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roine Strandberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Apollofjäril</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108971742</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skoghall, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6433116</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108974594</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skoghall, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>585817</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6433198</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>109513989</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 51923, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585527</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6433553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>109514010</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 51923, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585605</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433461</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>109514029</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 51923, Edsbruk, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585673</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433437</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
